--- a/result/xlsx/ecg_rocauc.xlsx
+++ b/result/xlsx/ecg_rocauc.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>feature</t>
   </si>
@@ -40,58 +40,58 @@
     <t>ratio_cwt_power</t>
   </si>
   <si>
+    <t>sample_entropy</t>
+  </si>
+  <si>
+    <t>permutation_entropy</t>
+  </si>
+  <si>
+    <t>shannon_entropy</t>
+  </si>
+  <si>
+    <t>cwt_freq</t>
+  </si>
+  <si>
     <t>skewness</t>
   </si>
   <si>
-    <t>sample_entropy</t>
+    <t>RMS40_mkV</t>
+  </si>
+  <si>
+    <t>fQRS_ms</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>phase_instability</t>
+  </si>
+  <si>
+    <t>max_psd_freq</t>
+  </si>
+  <si>
+    <t>cwt_time</t>
+  </si>
+  <si>
+    <t>max_psd_psd</t>
+  </si>
+  <si>
+    <t>ratio_psd_power</t>
+  </si>
+  <si>
+    <t>LAS_ms</t>
+  </si>
+  <si>
+    <t>QRSoff</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
   </si>
   <si>
     <t>std</t>
   </si>
   <si>
-    <t>permutation_entropy</t>
-  </si>
-  <si>
-    <t>shannon_entropy</t>
-  </si>
-  <si>
-    <t>cwt_freq</t>
-  </si>
-  <si>
-    <t>RMS40_mkV</t>
-  </si>
-  <si>
-    <t>fQRS_ms</t>
-  </si>
-  <si>
-    <t>phase_instability</t>
-  </si>
-  <si>
-    <t>max_psd_freq</t>
-  </si>
-  <si>
-    <t>cwt_time</t>
-  </si>
-  <si>
-    <t>max_psd_psd</t>
-  </si>
-  <si>
-    <t>ratio_psd_power</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>LAS_ms</t>
-  </si>
-  <si>
-    <t>QRSoff</t>
-  </si>
-  <si>
     <t>QRSon</t>
-  </si>
-  <si>
-    <t>kurtosis</t>
   </si>
   <si>
     <t>inf</t>
@@ -494,16 +494,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.6049382716049383</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C4">
-        <v>-1.136689277085605</v>
+        <v>0.5672737969392552</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="E4">
-        <v>0.3333333333333334</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F4">
         <v>0.3333333333333335</v>
@@ -514,19 +514,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.5802469135802469</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="C5">
-        <v>0.9413055672637527</v>
+        <v>1.157432529486824</v>
       </c>
       <c r="D5">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F5">
-        <v>0.3333333333333333</v>
+        <v>0.3333333333333335</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -534,19 +534,19 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.5679012345679013</v>
-      </c>
-      <c r="C6">
-        <v>0.0257236863352771</v>
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -554,19 +554,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="C7">
-        <v>1.199444772579061</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0.3333333333333335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -574,19 +574,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
+        <v>0.4320987654320988</v>
+      </c>
+      <c r="C8">
+        <v>0.8579322715742234</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -594,19 +594,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
+        <v>0.4320987654320987</v>
+      </c>
+      <c r="C9">
+        <v>0.003760057799617352</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.3333333333333335</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -614,19 +614,19 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.4320987654320987</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="C10">
-        <v>0.003760057799617352</v>
+        <v>37.92</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E10">
-        <v>0.3333333333333334</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F10">
-        <v>0.3333333333333335</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -634,16 +634,16 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>0.4197530864197531</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="C11">
-        <v>37.92</v>
+        <v>2.727161734355893E-05</v>
       </c>
       <c r="D11">
-        <v>0.5555555555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E11">
-        <v>0.5555555555555556</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F11">
         <v>0.1111111111111112</v>
@@ -754,7 +754,7 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>0.2962962962962963</v>
+        <v>0.2901234567901235</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
@@ -794,7 +794,7 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>0.2901234567901235</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -814,19 +814,19 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>0.2654320987654321</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
+        <v>0.2716049382716049</v>
+      </c>
+      <c r="C20">
+        <v>0.003390367151012191</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -834,7 +834,7 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.08641975308641975</v>
+        <v>0.2654320987654321</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>

--- a/result/xlsx/ecg_rocauc.xlsx
+++ b/result/xlsx/ecg_rocauc.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>feature</t>
   </si>
@@ -43,30 +43,30 @@
     <t>sample_entropy</t>
   </si>
   <si>
+    <t>shannon_entropy</t>
+  </si>
+  <si>
     <t>permutation_entropy</t>
   </si>
   <si>
-    <t>shannon_entropy</t>
-  </si>
-  <si>
     <t>cwt_freq</t>
   </si>
   <si>
+    <t>RMS40_mkV</t>
+  </si>
+  <si>
+    <t>fQRS_ms</t>
+  </si>
+  <si>
     <t>skewness</t>
   </si>
   <si>
-    <t>RMS40_mkV</t>
-  </si>
-  <si>
-    <t>fQRS_ms</t>
+    <t>phase_instability</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>phase_instability</t>
-  </si>
-  <si>
     <t>max_psd_freq</t>
   </si>
   <si>
@@ -76,6 +76,9 @@
     <t>max_psd_psd</t>
   </si>
   <si>
+    <t>QRSon</t>
+  </si>
+  <si>
     <t>ratio_psd_power</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>std</t>
-  </si>
-  <si>
-    <t>QRSon</t>
   </si>
   <si>
     <t>inf</t>
@@ -457,7 +457,7 @@
         <v>0.6790123456790124</v>
       </c>
       <c r="C2">
-        <v>1.902692101579325</v>
+        <v>1.903101624284804</v>
       </c>
       <c r="D2">
         <v>0.7777777777777778</v>
@@ -477,7 +477,7 @@
         <v>0.6419753086419753</v>
       </c>
       <c r="C3">
-        <v>0.001881086486130078</v>
+        <v>0.001869497199871253</v>
       </c>
       <c r="D3">
         <v>0.5555555555555556</v>
@@ -494,19 +494,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.5555555555555556</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="C4">
-        <v>0.5672737969392552</v>
+        <v>0.5792640388409001</v>
       </c>
       <c r="D4">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E4">
         <v>0.5555555555555556</v>
       </c>
       <c r="F4">
-        <v>0.3333333333333335</v>
+        <v>0.2222222222222223</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -514,19 +514,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.5185185185185185</v>
-      </c>
-      <c r="C5">
-        <v>1.157432529486824</v>
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0.3333333333333334</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0.3333333333333335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -534,19 +534,19 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
+        <v>0.4938271604938272</v>
+      </c>
+      <c r="C6">
+        <v>1.158401032305496</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.2222222222222223</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -574,19 +574,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.4320987654320988</v>
+        <v>0.4320987654320987</v>
       </c>
       <c r="C8">
-        <v>0.8579322715742234</v>
+        <v>0.004648959205415257</v>
       </c>
       <c r="D8">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F8">
-        <v>0.1111111111111112</v>
+        <v>0.3333333333333335</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -594,19 +594,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.4320987654320987</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="C9">
-        <v>0.003760057799617352</v>
+        <v>37.92</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E9">
-        <v>0.3333333333333334</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F9">
-        <v>0.3333333333333335</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -614,16 +614,16 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.4197530864197531</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="C10">
-        <v>37.92</v>
+        <v>-0.7095482207435488</v>
       </c>
       <c r="D10">
-        <v>0.5555555555555556</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E10">
-        <v>0.5555555555555556</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="F10">
         <v>0.1111111111111112</v>
@@ -637,16 +637,16 @@
         <v>0.4074074074074074</v>
       </c>
       <c r="C11">
-        <v>2.727161734355893E-05</v>
+        <v>-1.246724426806768</v>
       </c>
       <c r="D11">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0.4444444444444444</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="F11">
-        <v>0.1111111111111112</v>
+        <v>0.2222222222222223</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -654,19 +654,19 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>0.4074074074074074</v>
+        <v>0.3950617283950617</v>
       </c>
       <c r="C12">
-        <v>-1.243262006089833</v>
+        <v>2.414069538167809E-05</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E12">
-        <v>0.2222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F12">
-        <v>0.2222222222222223</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -674,19 +674,19 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>0.3950617283950617</v>
+        <v>0.382716049382716</v>
       </c>
       <c r="C13">
         <v>312.5</v>
       </c>
       <c r="D13">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E13">
         <v>0.4444444444444444</v>
       </c>
       <c r="F13">
-        <v>0.2222222222222223</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -717,7 +717,7 @@
         <v>0.3580246913580247</v>
       </c>
       <c r="C15">
-        <v>5.467928470434647E-11</v>
+        <v>5.873634700480806E-11</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -734,16 +734,16 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>0.345679012345679</v>
+        <v>0.3580246913580247</v>
       </c>
       <c r="C16">
-        <v>2.061278578795905E-06</v>
+        <v>314</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="E16">
-        <v>0.1111111111111112</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>0.1111111111111112</v>
@@ -754,19 +754,19 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>0.2901234567901235</v>
-      </c>
-      <c r="C17" t="s">
-        <v>26</v>
+        <v>0.345679012345679</v>
+      </c>
+      <c r="C17">
+        <v>2.162577157415963E-06</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -774,7 +774,7 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>0.2901234567901235</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="C18" t="s">
         <v>26</v>
@@ -816,17 +816,17 @@
       <c r="B20">
         <v>0.2716049382716049</v>
       </c>
-      <c r="C20">
-        <v>0.003390367151012191</v>
+      <c r="C20" t="s">
+        <v>26</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.1111111111111112</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>0.1111111111111112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -834,19 +834,19 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.2654320987654321</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
+        <v>0.2592592592592593</v>
+      </c>
+      <c r="C21">
+        <v>0.003419219182383382</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
   </sheetData>
